--- a/AAII_Financials/Yearly/ARBK_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ARBK_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 

--- a/AAII_Financials/Yearly/ARBK_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ARBK_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="92">
   <si>
     <t>ARBK</t>
   </si>
@@ -656,148 +656,160 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:L102"/>
+  <dimension ref="A5:M102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="11" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="12" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="J7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="L7" s="2"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="M7" s="2"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>47400</v>
+        <v>50600</v>
       </c>
       <c r="E8" s="3">
+        <v>58600</v>
+      </c>
+      <c r="F8" s="3">
         <v>74200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>19000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>8600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>800</v>
       </c>
-      <c r="I8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L8" s="3"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M8" s="3"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>81800</v>
+        <v>46700</v>
       </c>
       <c r="E9" s="3">
+        <v>101200</v>
+      </c>
+      <c r="F9" s="3">
         <v>20600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>15000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>5600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1200</v>
       </c>
-      <c r="I9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L9" s="3"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M9" s="3"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>-34500</v>
+        <v>3800</v>
       </c>
       <c r="E10" s="3">
+        <v>-42600</v>
+      </c>
+      <c r="F10" s="3">
         <v>53600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>3900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>3100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-400</v>
       </c>
-      <c r="I10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L10" s="3"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M10" s="3"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -810,26 +822,27 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E12" s="3">
         <v>100</v>
       </c>
-      <c r="E12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F12" s="3">
-        <v>0</v>
+      <c r="F12" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G12" s="3">
+        <v>0</v>
+      </c>
+      <c r="H12" s="3">
         <v>100</v>
       </c>
-      <c r="H12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I12" s="3" t="s">
         <v>3</v>
       </c>
@@ -839,9 +852,12 @@
       <c r="K12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L12" s="3"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M12" s="3"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -869,21 +885,24 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-      <c r="L13" s="3"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+      <c r="M13" s="3"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>49300</v>
+        <v>6900</v>
       </c>
       <c r="E14" s="3">
+        <v>128300</v>
+      </c>
+      <c r="F14" s="3">
         <v>-1000</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
       </c>
@@ -899,26 +918,29 @@
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L14" s="3"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M14" s="3"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>6900</v>
+        <v>1500</v>
       </c>
       <c r="E15" s="3">
+        <v>8500</v>
+      </c>
+      <c r="F15" s="3">
         <v>400</v>
-      </c>
-      <c r="F15" s="3">
-        <v>100</v>
       </c>
       <c r="G15" s="3">
         <v>100</v>
       </c>
-      <c r="H15" s="3" t="s">
-        <v>3</v>
+      <c r="H15" s="3">
+        <v>100</v>
       </c>
       <c r="I15" s="3" t="s">
         <v>3</v>
@@ -929,9 +951,12 @@
       <c r="K15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L15" s="3"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M15" s="3"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -941,68 +966,75 @@
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
-    </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>161900</v>
+        <v>71900</v>
       </c>
       <c r="E17" s="3">
+        <v>255700</v>
+      </c>
+      <c r="F17" s="3">
         <v>31400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>17400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>9500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>4900</v>
       </c>
-      <c r="I17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L17" s="3"/>
-    </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M17" s="3"/>
+    </row>
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-114500</v>
+        <v>-21300</v>
       </c>
       <c r="E18" s="3">
+        <v>-197100</v>
+      </c>
+      <c r="F18" s="3">
         <v>42800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-4100</v>
       </c>
-      <c r="I18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L18" s="3"/>
-    </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M18" s="3"/>
+    </row>
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1015,28 +1047,29 @@
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
-    </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-61700</v>
+        <v>-2100</v>
       </c>
       <c r="E20" s="3">
+        <v>-20900</v>
+      </c>
+      <c r="F20" s="3">
         <v>-1400</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
       <c r="G20" s="3">
         <v>0</v>
       </c>
       <c r="H20" s="3">
         <v>0</v>
       </c>
-      <c r="I20" s="3" t="s">
-        <v>3</v>
+      <c r="I20" s="3">
+        <v>0</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>3</v>
@@ -1044,59 +1077,65 @@
       <c r="K20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L20" s="3"/>
-    </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M20" s="3"/>
+    </row>
+    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-152800</v>
+        <v>-3300</v>
       </c>
       <c r="E21" s="3">
+        <v>-194600</v>
+      </c>
+      <c r="F21" s="3">
         <v>52900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>7600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-3600</v>
       </c>
-      <c r="I21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L21" s="3"/>
-    </row>
-    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M21" s="3"/>
+    </row>
+    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>18300</v>
+        <v>11600</v>
       </c>
       <c r="E22" s="3">
+        <v>22700</v>
+      </c>
+      <c r="F22" s="3">
         <v>2100</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>200</v>
       </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
       <c r="H22" s="3">
         <v>0</v>
       </c>
-      <c r="I22" s="3" t="s">
-        <v>3</v>
+      <c r="I22" s="3">
+        <v>0</v>
       </c>
       <c r="J22" s="3" t="s">
         <v>3</v>
@@ -1104,59 +1143,65 @@
       <c r="K22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L22" s="3"/>
-    </row>
-    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M22" s="3"/>
+    </row>
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-194600</v>
+        <v>-35000</v>
       </c>
       <c r="E23" s="3">
+        <v>-240700</v>
+      </c>
+      <c r="F23" s="3">
         <v>39300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-4100</v>
       </c>
-      <c r="I23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L23" s="3"/>
-    </row>
-    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M23" s="3"/>
+    </row>
+    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>-400</v>
+        <v>0</v>
       </c>
       <c r="E24" s="3">
+        <v>-11700</v>
+      </c>
+      <c r="F24" s="3">
         <v>8500</v>
       </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>3</v>
+      <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I24" s="3">
+        <v>0</v>
       </c>
       <c r="J24" s="3" t="s">
         <v>3</v>
@@ -1164,9 +1209,12 @@
       <c r="K24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L24" s="3"/>
-    </row>
-    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M24" s="3"/>
+    </row>
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1194,69 +1242,78 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-      <c r="L25" s="3"/>
-    </row>
-    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+      <c r="M25" s="3"/>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-194200</v>
+        <v>-35000</v>
       </c>
       <c r="E26" s="3">
+        <v>-229000</v>
+      </c>
+      <c r="F26" s="3">
         <v>30800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-4100</v>
       </c>
-      <c r="I26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L26" s="3"/>
-    </row>
-    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M26" s="3"/>
+    </row>
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-194200</v>
+        <v>-35000</v>
       </c>
       <c r="E27" s="3">
+        <v>-229000</v>
+      </c>
+      <c r="F27" s="3">
         <v>30800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-4100</v>
       </c>
-      <c r="I27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L27" s="3"/>
-    </row>
-    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M27" s="3"/>
+    </row>
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1284,9 +1341,12 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-      <c r="L28" s="3"/>
-    </row>
-    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+      <c r="M28" s="3"/>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1314,9 +1374,12 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3"/>
-    </row>
-    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3"/>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1344,9 +1407,12 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-      <c r="L30" s="3"/>
-    </row>
-    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+      <c r="M30" s="3"/>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1374,29 +1440,32 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-      <c r="L31" s="3"/>
-    </row>
-    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+      <c r="M31" s="3"/>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>61700</v>
+        <v>2100</v>
       </c>
       <c r="E32" s="3">
+        <v>20900</v>
+      </c>
+      <c r="F32" s="3">
         <v>1400</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
       <c r="G32" s="3">
         <v>0</v>
       </c>
       <c r="H32" s="3">
         <v>0</v>
       </c>
-      <c r="I32" s="3" t="s">
-        <v>3</v>
+      <c r="I32" s="3">
+        <v>0</v>
       </c>
       <c r="J32" s="3" t="s">
         <v>3</v>
@@ -1404,39 +1473,45 @@
       <c r="K32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L32" s="3"/>
-    </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M32" s="3"/>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-194200</v>
+        <v>-35000</v>
       </c>
       <c r="E33" s="3">
+        <v>-229000</v>
+      </c>
+      <c r="F33" s="3">
         <v>30800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-4100</v>
       </c>
-      <c r="I33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L33" s="3"/>
-    </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M33" s="3"/>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1464,74 +1539,83 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-      <c r="L34" s="3"/>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+      <c r="M34" s="3"/>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-194200</v>
+        <v>-35000</v>
       </c>
       <c r="E35" s="3">
+        <v>-229000</v>
+      </c>
+      <c r="F35" s="3">
         <v>30800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-4100</v>
       </c>
-      <c r="I35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L35" s="3"/>
-    </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M35" s="3"/>
+    </row>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="J38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="K38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="L38" s="2"/>
-    </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="M38" s="2"/>
+    </row>
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1544,8 +1628,9 @@
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1558,38 +1643,42 @@
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>7400</v>
+      </c>
+      <c r="E41" s="3">
         <v>20100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>11800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>16400</v>
       </c>
-      <c r="I41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J41" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L41" s="3"/>
-    </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M41" s="3"/>
+    </row>
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1617,39 +1706,45 @@
       <c r="K42" s="3">
         <v>0</v>
       </c>
-      <c r="L42" s="3"/>
-    </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3"/>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E43" s="3">
         <v>800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2200</v>
       </c>
-      <c r="I43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J43" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L43" s="3"/>
-    </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M43" s="3"/>
+    </row>
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1677,29 +1772,32 @@
       <c r="K44" s="3">
         <v>0</v>
       </c>
-      <c r="L44" s="3"/>
-    </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L44" s="3">
+        <v>0</v>
+      </c>
+      <c r="M44" s="3"/>
+    </row>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E45" s="3">
         <v>6400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>141400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>5400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1000</v>
       </c>
-      <c r="H45" s="3">
-        <v>0</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>3</v>
+      <c r="I45" s="3">
+        <v>0</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>3</v>
@@ -1707,57 +1805,63 @@
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L45" s="3"/>
-    </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M45" s="3"/>
+    </row>
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>14900</v>
+      </c>
+      <c r="E46" s="3">
         <v>27300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>155900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>8900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>3300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>18600</v>
       </c>
-      <c r="I46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J46" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L46" s="3"/>
-    </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M46" s="3"/>
+    </row>
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>400</v>
+      </c>
+      <c r="E47" s="3">
         <v>3300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>14200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>5500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>5600</v>
       </c>
-      <c r="H47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I47" s="3" t="s">
         <v>3</v>
       </c>
@@ -1767,69 +1871,78 @@
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L47" s="3"/>
-    </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M47" s="3"/>
+    </row>
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>59700</v>
+      </c>
+      <c r="E48" s="3">
         <v>141400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>112000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>17900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>15400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2500</v>
       </c>
-      <c r="I48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J48" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L48" s="3"/>
-    </row>
-    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M48" s="3"/>
+    </row>
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>900</v>
+      </c>
+      <c r="E49" s="3">
         <v>2100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>5600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>600</v>
       </c>
-      <c r="I49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J49" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L49" s="3"/>
-    </row>
-    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M49" s="3"/>
+    </row>
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1857,9 +1970,12 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-      <c r="L50" s="3"/>
-    </row>
-    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+      <c r="M50" s="3"/>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1887,9 +2003,12 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-      <c r="L51" s="3"/>
-    </row>
-    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+      <c r="M51" s="3"/>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -1917,9 +2036,12 @@
       <c r="K52" s="3">
         <v>0</v>
       </c>
-      <c r="L52" s="3"/>
-    </row>
-    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L52" s="3">
+        <v>0</v>
+      </c>
+      <c r="M52" s="3"/>
+    </row>
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1947,39 +2069,45 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-      <c r="L53" s="3"/>
-    </row>
-    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+      <c r="M53" s="3"/>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>75900</v>
+      </c>
+      <c r="E54" s="3">
         <v>110200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>287700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>32600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>24700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>21600</v>
       </c>
-      <c r="I54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J54" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L54" s="3"/>
-    </row>
-    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M54" s="3"/>
+    </row>
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1992,8 +2120,9 @@
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
-    </row>
-    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2006,56 +2135,60 @@
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
-    </row>
-    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E57" s="3">
         <v>3200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>10300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>200</v>
       </c>
-      <c r="I57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J57" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L57" s="3"/>
-    </row>
-    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M57" s="3"/>
+    </row>
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>14300</v>
+      </c>
+      <c r="E58" s="3">
         <v>11600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>23400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1100</v>
       </c>
-      <c r="H58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2065,27 +2198,30 @@
       <c r="K58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L58" s="3"/>
-    </row>
-    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M58" s="3"/>
+    </row>
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>10900</v>
+      </c>
+      <c r="E59" s="3">
         <v>9400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>21000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>400</v>
       </c>
-      <c r="H59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2095,54 +2231,60 @@
       <c r="K59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L59" s="3"/>
-    </row>
-    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M59" s="3"/>
+    </row>
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>27600</v>
+      </c>
+      <c r="E60" s="3">
         <v>24300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>54700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>4400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>4000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>200</v>
       </c>
-      <c r="I60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J60" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L60" s="3"/>
-    </row>
-    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M60" s="3"/>
+    </row>
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>48200</v>
+      </c>
+      <c r="E61" s="3">
         <v>64300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>30700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>3900</v>
       </c>
-      <c r="G61" s="3">
-        <v>0</v>
-      </c>
       <c r="H61" s="3">
         <v>0</v>
       </c>
@@ -2155,21 +2297,24 @@
       <c r="K61" s="3">
         <v>0</v>
       </c>
-      <c r="L61" s="3"/>
-    </row>
-    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L61" s="3">
+        <v>0</v>
+      </c>
+      <c r="M61" s="3"/>
+    </row>
+    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>0</v>
+      </c>
+      <c r="E62" s="3">
         <v>7900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>500</v>
       </c>
-      <c r="F62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2185,9 +2330,12 @@
       <c r="K62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L62" s="3"/>
-    </row>
-    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M62" s="3"/>
+    </row>
+    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2215,9 +2363,12 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-      <c r="L63" s="3"/>
-    </row>
-    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+      <c r="M63" s="3"/>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2245,9 +2396,12 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-      <c r="L64" s="3"/>
-    </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+      <c r="M64" s="3"/>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2275,39 +2429,45 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-      <c r="L65" s="3"/>
-    </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+      <c r="M65" s="3"/>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>75800</v>
+      </c>
+      <c r="E66" s="3">
         <v>96500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>85900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>8300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>200</v>
       </c>
-      <c r="I66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J66" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L66" s="3"/>
-    </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M66" s="3"/>
+    </row>
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2320,8 +2480,9 @@
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
-    </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2349,9 +2510,12 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-      <c r="L68" s="3"/>
-    </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+      <c r="M68" s="3"/>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2379,9 +2543,12 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-      <c r="L69" s="3"/>
-    </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+      <c r="M69" s="3"/>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2409,9 +2576,12 @@
       <c r="K70" s="3">
         <v>0</v>
       </c>
-      <c r="L70" s="3"/>
-    </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3"/>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2439,39 +2609,45 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-      <c r="L71" s="3"/>
-    </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+      <c r="M71" s="3"/>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-180200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-160100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>54700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>22000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-5000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-4100</v>
       </c>
-      <c r="I72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J72" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L72" s="3"/>
-    </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M72" s="3"/>
+    </row>
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2499,9 +2675,12 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-      <c r="L73" s="3"/>
-    </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+      <c r="M73" s="3"/>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2529,9 +2708,12 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-      <c r="L74" s="3"/>
-    </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+      <c r="M74" s="3"/>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2559,39 +2741,45 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-      <c r="L75" s="3"/>
-    </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+      <c r="M75" s="3"/>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>200</v>
+      </c>
+      <c r="E76" s="3">
         <v>13700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>201800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>24300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>20700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>21400</v>
       </c>
-      <c r="I76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J76" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L76" s="3"/>
-    </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M76" s="3"/>
+    </row>
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2619,74 +2807,83 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-      <c r="L77" s="3"/>
-    </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+      <c r="M77" s="3"/>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="J80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="K80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="L80" s="2"/>
-    </row>
-    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="M80" s="2"/>
+    </row>
+    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-194200</v>
+        <v>-35000</v>
       </c>
       <c r="E81" s="3">
+        <v>-229000</v>
+      </c>
+      <c r="F81" s="3">
         <v>30800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-4100</v>
       </c>
-      <c r="I81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L81" s="3"/>
-    </row>
-    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M81" s="3"/>
+    </row>
+    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2699,38 +2896,42 @@
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
-    </row>
-    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>20100</v>
+      </c>
+      <c r="E83" s="3">
         <v>23400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>11500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>6000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>2200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>500</v>
       </c>
-      <c r="I83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L83" s="3"/>
-    </row>
-    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M83" s="3"/>
+    </row>
+    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2758,9 +2959,12 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-      <c r="L84" s="3"/>
-    </row>
-    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+      <c r="M84" s="3"/>
+    </row>
+    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2788,9 +2992,12 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-      <c r="L85" s="3"/>
-    </row>
-    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+      <c r="M85" s="3"/>
+    </row>
+    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2818,9 +3025,12 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-      <c r="L86" s="3"/>
-    </row>
-    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+      <c r="M86" s="3"/>
+    </row>
+    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2848,9 +3058,12 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-      <c r="L87" s="3"/>
-    </row>
-    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+      <c r="M87" s="3"/>
+    </row>
+    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2878,39 +3091,45 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-      <c r="L88" s="3"/>
-    </row>
-    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+      <c r="M88" s="3"/>
+    </row>
+    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E89" s="3">
         <v>-70700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-27800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>2400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-5200</v>
       </c>
-      <c r="I89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L89" s="3"/>
-    </row>
-    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M89" s="3"/>
+    </row>
+    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2923,38 +3142,42 @@
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
-    </row>
-    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-87400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-126400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-15000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2900</v>
       </c>
-      <c r="I91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L91" s="3"/>
-    </row>
-    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M91" s="3"/>
+    </row>
+    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2982,9 +3205,12 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-      <c r="L92" s="3"/>
-    </row>
-    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+      <c r="M92" s="3"/>
+    </row>
+    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3012,39 +3238,45 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-      <c r="L93" s="3"/>
-    </row>
-    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+      <c r="M93" s="3"/>
+    </row>
+    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E94" s="3">
         <v>5500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-137600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-16700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-3900</v>
       </c>
-      <c r="I94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L94" s="3"/>
-    </row>
-    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M94" s="3"/>
+    </row>
+    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3057,8 +3289,9 @@
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
-    </row>
-    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3086,9 +3319,12 @@
       <c r="K96" s="3">
         <v>0</v>
       </c>
-      <c r="L96" s="3"/>
-    </row>
-    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3"/>
+    </row>
+    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3116,9 +3352,12 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-      <c r="L97" s="3"/>
-    </row>
-    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+      <c r="M97" s="3"/>
+    </row>
+    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3146,9 +3385,12 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-      <c r="L98" s="3"/>
-    </row>
-    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+      <c r="M98" s="3"/>
+    </row>
+    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3176,48 +3418,54 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-      <c r="L99" s="3"/>
-    </row>
-    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+      <c r="M99" s="3"/>
+    </row>
+    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-15800</v>
+      </c>
+      <c r="E100" s="3">
         <v>68100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>175100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>25500</v>
       </c>
-      <c r="I100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L100" s="3"/>
-    </row>
-    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M100" s="3"/>
+    </row>
+    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>400</v>
+      </c>
+      <c r="E101" s="3">
         <v>1900</v>
       </c>
-      <c r="E101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F101" s="3" t="s">
         <v>3</v>
       </c>
@@ -3233,40 +3481,46 @@
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
-      <c r="L101" s="3"/>
-    </row>
-    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="K101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L101" s="3">
+        <v>0</v>
+      </c>
+      <c r="M101" s="3"/>
+    </row>
+    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-12600</v>
+      </c>
+      <c r="E102" s="3">
         <v>4900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>9800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-16200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>16400</v>
       </c>
-      <c r="I102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L102" s="3"/>
+      <c r="L102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/ARBK_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ARBK_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="92">
   <si>
     <t>ARBK</t>
   </si>
@@ -721,16 +721,16 @@
         <v>58600</v>
       </c>
       <c r="F8" s="3">
-        <v>74200</v>
+        <v>100500</v>
       </c>
       <c r="G8" s="3">
-        <v>19000</v>
+        <v>25900</v>
       </c>
       <c r="H8" s="3">
-        <v>8600</v>
+        <v>11400</v>
       </c>
       <c r="I8" s="3">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>3</v>
@@ -748,22 +748,22 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>46700</v>
+        <v>29300</v>
       </c>
       <c r="E9" s="3">
-        <v>101200</v>
+        <v>27800</v>
       </c>
       <c r="F9" s="3">
-        <v>20600</v>
+        <v>31000</v>
       </c>
       <c r="G9" s="3">
-        <v>15000</v>
+        <v>15400</v>
       </c>
       <c r="H9" s="3">
-        <v>5600</v>
+        <v>4600</v>
       </c>
       <c r="I9" s="3">
-        <v>1200</v>
+        <v>1500</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>3</v>
@@ -781,22 +781,22 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>3800</v>
+        <v>21300</v>
       </c>
       <c r="E10" s="3">
-        <v>-42600</v>
+        <v>30800</v>
       </c>
       <c r="F10" s="3">
-        <v>53600</v>
+        <v>69500</v>
       </c>
       <c r="G10" s="3">
-        <v>3900</v>
+        <v>10500</v>
       </c>
       <c r="H10" s="3">
-        <v>3100</v>
+        <v>6800</v>
       </c>
       <c r="I10" s="3">
-        <v>-400</v>
+        <v>-500</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>3</v>
@@ -832,7 +832,7 @@
         <v>3</v>
       </c>
       <c r="E12" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>3</v>
@@ -895,13 +895,13 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>6900</v>
+        <v>3700</v>
       </c>
       <c r="E14" s="3">
-        <v>128300</v>
+        <v>135100</v>
       </c>
       <c r="F14" s="3">
-        <v>-1000</v>
+        <v>500</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
@@ -928,25 +928,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>1500</v>
+        <v>18700</v>
       </c>
       <c r="E15" s="3">
-        <v>8500</v>
+        <v>20500</v>
       </c>
       <c r="F15" s="3">
-        <v>400</v>
+        <v>11000</v>
       </c>
       <c r="G15" s="3">
+        <v>8000</v>
+      </c>
+      <c r="H15" s="3">
+        <v>2800</v>
+      </c>
+      <c r="I15" s="3">
         <v>100</v>
       </c>
-      <c r="H15" s="3">
-        <v>100</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>3</v>
+      <c r="J15" s="3">
+        <v>0</v>
       </c>
       <c r="K15" s="3" t="s">
         <v>3</v>
@@ -973,22 +973,22 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>71900</v>
+        <v>70000</v>
       </c>
       <c r="E17" s="3">
-        <v>255700</v>
+        <v>139300</v>
       </c>
       <c r="F17" s="3">
-        <v>31400</v>
+        <v>42200</v>
       </c>
       <c r="G17" s="3">
-        <v>17400</v>
+        <v>23300</v>
       </c>
       <c r="H17" s="3">
-        <v>9500</v>
+        <v>12300</v>
       </c>
       <c r="I17" s="3">
-        <v>4900</v>
+        <v>5000</v>
       </c>
       <c r="J17" s="3" t="s">
         <v>3</v>
@@ -1006,22 +1006,22 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-21300</v>
+        <v>-19400</v>
       </c>
       <c r="E18" s="3">
-        <v>-197100</v>
+        <v>-80700</v>
       </c>
       <c r="F18" s="3">
-        <v>42800</v>
+        <v>58200</v>
       </c>
       <c r="G18" s="3">
-        <v>1600</v>
+        <v>2600</v>
       </c>
       <c r="H18" s="3">
-        <v>-800</v>
+        <v>-900</v>
       </c>
       <c r="I18" s="3">
-        <v>-4100</v>
+        <v>-3700</v>
       </c>
       <c r="J18" s="3" t="s">
         <v>3</v>
@@ -1054,22 +1054,22 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-2100</v>
+        <v>400</v>
       </c>
       <c r="E20" s="3">
-        <v>-20900</v>
+        <v>2300</v>
       </c>
       <c r="F20" s="3">
-        <v>-1400</v>
+        <v>1600</v>
       </c>
       <c r="G20" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="H20" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I20" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>3</v>
@@ -1087,25 +1087,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-3300</v>
+        <v>-1100</v>
       </c>
       <c r="E21" s="3">
-        <v>-194600</v>
+        <v>-62500</v>
       </c>
       <c r="F21" s="3">
-        <v>52900</v>
+        <v>67600</v>
       </c>
       <c r="G21" s="3">
-        <v>7600</v>
+        <v>10200</v>
       </c>
       <c r="H21" s="3">
-        <v>1400</v>
+        <v>1700</v>
       </c>
       <c r="I21" s="3">
-        <v>-3600</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>3</v>
+        <v>-4800</v>
+      </c>
+      <c r="J21" s="3">
+        <v>0</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>3</v>
@@ -1126,13 +1126,13 @@
         <v>22700</v>
       </c>
       <c r="F22" s="3">
-        <v>2100</v>
+        <v>2900</v>
       </c>
       <c r="G22" s="3">
         <v>200</v>
       </c>
       <c r="H22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I22" s="3">
         <v>0</v>
@@ -1159,16 +1159,16 @@
         <v>-240700</v>
       </c>
       <c r="F23" s="3">
-        <v>39300</v>
+        <v>53200</v>
       </c>
       <c r="G23" s="3">
-        <v>1400</v>
+        <v>2000</v>
       </c>
       <c r="H23" s="3">
-        <v>-900</v>
+        <v>-1200</v>
       </c>
       <c r="I23" s="3">
-        <v>-4100</v>
+        <v>-4800</v>
       </c>
       <c r="J23" s="3" t="s">
         <v>3</v>
@@ -1185,23 +1185,23 @@
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E24" s="3">
         <v>-11700</v>
       </c>
       <c r="F24" s="3">
-        <v>8500</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
+        <v>11500</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I24" s="3">
-        <v>0</v>
+      <c r="I24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J24" s="3" t="s">
         <v>3</v>
@@ -1258,16 +1258,16 @@
         <v>-229000</v>
       </c>
       <c r="F26" s="3">
-        <v>30800</v>
+        <v>41700</v>
       </c>
       <c r="G26" s="3">
-        <v>1400</v>
+        <v>2000</v>
       </c>
       <c r="H26" s="3">
-        <v>-900</v>
+        <v>-1200</v>
       </c>
       <c r="I26" s="3">
-        <v>-4100</v>
+        <v>-4800</v>
       </c>
       <c r="J26" s="3" t="s">
         <v>3</v>
@@ -1291,16 +1291,16 @@
         <v>-229000</v>
       </c>
       <c r="F27" s="3">
-        <v>30800</v>
+        <v>41700</v>
       </c>
       <c r="G27" s="3">
-        <v>1400</v>
+        <v>2000</v>
       </c>
       <c r="H27" s="3">
-        <v>-900</v>
+        <v>-1100</v>
       </c>
       <c r="I27" s="3">
-        <v>-4100</v>
+        <v>-4800</v>
       </c>
       <c r="J27" s="3" t="s">
         <v>3</v>
@@ -1450,22 +1450,22 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>2100</v>
+        <v>-400</v>
       </c>
       <c r="E32" s="3">
-        <v>20900</v>
+        <v>-2300</v>
       </c>
       <c r="F32" s="3">
-        <v>1400</v>
+        <v>-1600</v>
       </c>
       <c r="G32" s="3">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="H32" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="I32" s="3">
-        <v>0</v>
+        <v>-1200</v>
       </c>
       <c r="J32" s="3" t="s">
         <v>3</v>
@@ -1489,16 +1489,16 @@
         <v>-229000</v>
       </c>
       <c r="F33" s="3">
-        <v>30800</v>
+        <v>41700</v>
       </c>
       <c r="G33" s="3">
-        <v>1400</v>
+        <v>2000</v>
       </c>
       <c r="H33" s="3">
-        <v>-900</v>
+        <v>-1200</v>
       </c>
       <c r="I33" s="3">
-        <v>-4100</v>
+        <v>-4800</v>
       </c>
       <c r="J33" s="3" t="s">
         <v>3</v>
@@ -1555,16 +1555,16 @@
         <v>-229000</v>
       </c>
       <c r="F35" s="3">
-        <v>30800</v>
+        <v>41700</v>
       </c>
       <c r="G35" s="3">
-        <v>1400</v>
+        <v>2000</v>
       </c>
       <c r="H35" s="3">
-        <v>-900</v>
+        <v>-1200</v>
       </c>
       <c r="I35" s="3">
-        <v>-4100</v>
+        <v>-4800</v>
       </c>
       <c r="J35" s="3" t="s">
         <v>3</v>
@@ -1656,16 +1656,16 @@
         <v>20100</v>
       </c>
       <c r="F41" s="3">
-        <v>11800</v>
+        <v>16000</v>
       </c>
       <c r="G41" s="3">
-        <v>2100</v>
+        <v>2800</v>
       </c>
       <c r="H41" s="3">
         <v>200</v>
       </c>
       <c r="I41" s="3">
-        <v>16400</v>
+        <v>20900</v>
       </c>
       <c r="J41" s="3" t="s">
         <v>3</v>
@@ -1722,16 +1722,16 @@
         <v>800</v>
       </c>
       <c r="F43" s="3">
-        <v>2700</v>
+        <v>3700</v>
       </c>
       <c r="G43" s="3">
-        <v>1400</v>
+        <v>1900</v>
       </c>
       <c r="H43" s="3">
-        <v>2100</v>
+        <v>2400</v>
       </c>
       <c r="I43" s="3">
-        <v>2200</v>
+        <v>2800</v>
       </c>
       <c r="J43" s="3" t="s">
         <v>3</v>
@@ -1748,26 +1748,26 @@
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -1782,19 +1782,19 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>5000</v>
+        <v>3600</v>
       </c>
       <c r="E45" s="3">
-        <v>6400</v>
+        <v>400</v>
       </c>
       <c r="F45" s="3">
-        <v>141400</v>
+        <v>173600</v>
       </c>
       <c r="G45" s="3">
-        <v>5400</v>
+        <v>6300</v>
       </c>
       <c r="H45" s="3">
-        <v>1000</v>
+        <v>1400</v>
       </c>
       <c r="I45" s="3">
         <v>0</v>
@@ -1821,16 +1821,16 @@
         <v>27300</v>
       </c>
       <c r="F46" s="3">
-        <v>155900</v>
+        <v>211100</v>
       </c>
       <c r="G46" s="3">
-        <v>8900</v>
+        <v>12100</v>
       </c>
       <c r="H46" s="3">
-        <v>3300</v>
+        <v>4400</v>
       </c>
       <c r="I46" s="3">
-        <v>18600</v>
+        <v>23700</v>
       </c>
       <c r="J46" s="3" t="s">
         <v>3</v>
@@ -1854,13 +1854,13 @@
         <v>3300</v>
       </c>
       <c r="F47" s="3">
-        <v>14200</v>
+        <v>19300</v>
       </c>
       <c r="G47" s="3">
-        <v>5500</v>
+        <v>1900</v>
       </c>
       <c r="H47" s="3">
-        <v>5600</v>
+        <v>1900</v>
       </c>
       <c r="I47" s="3" t="s">
         <v>3</v>
@@ -1884,19 +1884,19 @@
         <v>59700</v>
       </c>
       <c r="E48" s="3">
-        <v>141400</v>
+        <v>77500</v>
       </c>
       <c r="F48" s="3">
-        <v>112000</v>
+        <v>151600</v>
       </c>
       <c r="G48" s="3">
-        <v>17900</v>
+        <v>24400</v>
       </c>
       <c r="H48" s="3">
-        <v>15400</v>
+        <v>20400</v>
       </c>
       <c r="I48" s="3">
-        <v>2500</v>
+        <v>3100</v>
       </c>
       <c r="J48" s="3" t="s">
         <v>3</v>
@@ -1920,16 +1920,16 @@
         <v>2100</v>
       </c>
       <c r="F49" s="3">
-        <v>5600</v>
+        <v>7600</v>
       </c>
       <c r="G49" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="H49" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="I49" s="3">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="J49" s="3" t="s">
         <v>3</v>
@@ -2012,26 +2012,26 @@
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>0</v>
-      </c>
-      <c r="E52" s="3">
-        <v>0</v>
-      </c>
-      <c r="F52" s="3">
-        <v>0</v>
+      <c r="D52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G52" s="3">
-        <v>0</v>
+        <v>5600</v>
       </c>
       <c r="H52" s="3">
-        <v>0</v>
-      </c>
-      <c r="I52" s="3">
-        <v>0</v>
-      </c>
-      <c r="J52" s="3">
-        <v>0</v>
+        <v>5500</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K52" s="3">
         <v>0</v>
@@ -2085,16 +2085,16 @@
         <v>110200</v>
       </c>
       <c r="F54" s="3">
-        <v>287700</v>
+        <v>389600</v>
       </c>
       <c r="G54" s="3">
-        <v>32600</v>
+        <v>44600</v>
       </c>
       <c r="H54" s="3">
-        <v>24700</v>
+        <v>32700</v>
       </c>
       <c r="I54" s="3">
-        <v>21600</v>
+        <v>27600</v>
       </c>
       <c r="J54" s="3" t="s">
         <v>3</v>
@@ -2145,19 +2145,19 @@
         <v>2300</v>
       </c>
       <c r="E57" s="3">
-        <v>3200</v>
+        <v>3100</v>
       </c>
       <c r="F57" s="3">
-        <v>10300</v>
+        <v>13900</v>
       </c>
       <c r="G57" s="3">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="H57" s="3">
-        <v>2500</v>
-      </c>
-      <c r="I57" s="3">
-        <v>200</v>
+        <v>3300</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J57" s="3" t="s">
         <v>3</v>
@@ -2181,16 +2181,16 @@
         <v>11600</v>
       </c>
       <c r="F58" s="3">
-        <v>23400</v>
+        <v>31700</v>
       </c>
       <c r="G58" s="3">
-        <v>3600</v>
+        <v>4900</v>
       </c>
       <c r="H58" s="3">
-        <v>1100</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>3</v>
+        <v>1400</v>
+      </c>
+      <c r="I58" s="3">
+        <v>0</v>
       </c>
       <c r="J58" s="3" t="s">
         <v>3</v>
@@ -2208,22 +2208,22 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>10900</v>
-      </c>
-      <c r="E59" s="3">
-        <v>9400</v>
+        <v>2100</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F59" s="3">
-        <v>21000</v>
-      </c>
-      <c r="G59" s="3">
-        <v>300</v>
+        <v>21700</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H59" s="3">
-        <v>400</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="I59" s="3">
+        <v>0</v>
       </c>
       <c r="J59" s="3" t="s">
         <v>3</v>
@@ -2244,19 +2244,19 @@
         <v>27600</v>
       </c>
       <c r="E60" s="3">
-        <v>24300</v>
+        <v>21400</v>
       </c>
       <c r="F60" s="3">
-        <v>54700</v>
+        <v>74000</v>
       </c>
       <c r="G60" s="3">
-        <v>4400</v>
+        <v>6000</v>
       </c>
       <c r="H60" s="3">
-        <v>4000</v>
+        <v>5300</v>
       </c>
       <c r="I60" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="J60" s="3" t="s">
         <v>3</v>
@@ -2280,10 +2280,10 @@
         <v>64300</v>
       </c>
       <c r="F61" s="3">
-        <v>30700</v>
+        <v>41500</v>
       </c>
       <c r="G61" s="3">
-        <v>3900</v>
+        <v>5300</v>
       </c>
       <c r="H61" s="3">
         <v>0</v>
@@ -2306,14 +2306,14 @@
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>0</v>
-      </c>
-      <c r="E62" s="3">
-        <v>7900</v>
-      </c>
-      <c r="F62" s="3">
-        <v>500</v>
+      <c r="D62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G62" s="3" t="s">
         <v>3</v>
@@ -2442,19 +2442,19 @@
         <v>75800</v>
       </c>
       <c r="E66" s="3">
-        <v>96500</v>
+        <v>85700</v>
       </c>
       <c r="F66" s="3">
-        <v>85900</v>
+        <v>116300</v>
       </c>
       <c r="G66" s="3">
-        <v>8300</v>
+        <v>11400</v>
       </c>
       <c r="H66" s="3">
-        <v>4000</v>
+        <v>5300</v>
       </c>
       <c r="I66" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="J66" s="3" t="s">
         <v>3</v>
@@ -2619,22 +2619,22 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-180200</v>
+        <v>-192400</v>
       </c>
       <c r="E72" s="3">
-        <v>-160100</v>
+        <v>-157300</v>
       </c>
       <c r="F72" s="3">
-        <v>54700</v>
+        <v>71500</v>
       </c>
       <c r="G72" s="3">
-        <v>22000</v>
+        <v>30000</v>
       </c>
       <c r="H72" s="3">
-        <v>-5000</v>
+        <v>-6600</v>
       </c>
       <c r="I72" s="3">
-        <v>-4100</v>
+        <v>-5200</v>
       </c>
       <c r="J72" s="3" t="s">
         <v>3</v>
@@ -2754,19 +2754,19 @@
         <v>200</v>
       </c>
       <c r="E76" s="3">
-        <v>13700</v>
+        <v>24600</v>
       </c>
       <c r="F76" s="3">
-        <v>201800</v>
+        <v>273300</v>
       </c>
       <c r="G76" s="3">
-        <v>24300</v>
+        <v>33200</v>
       </c>
       <c r="H76" s="3">
-        <v>20700</v>
+        <v>27500</v>
       </c>
       <c r="I76" s="3">
-        <v>21400</v>
+        <v>27300</v>
       </c>
       <c r="J76" s="3" t="s">
         <v>3</v>
@@ -2861,16 +2861,16 @@
         <v>-229000</v>
       </c>
       <c r="F81" s="3">
-        <v>30800</v>
+        <v>41700</v>
       </c>
       <c r="G81" s="3">
-        <v>1400</v>
+        <v>2000</v>
       </c>
       <c r="H81" s="3">
-        <v>-900</v>
+        <v>-1200</v>
       </c>
       <c r="I81" s="3">
-        <v>-4100</v>
+        <v>-4800</v>
       </c>
       <c r="J81" s="3" t="s">
         <v>3</v>
@@ -2903,22 +2903,22 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>20100</v>
+        <v>-91900</v>
       </c>
       <c r="E83" s="3">
-        <v>23400</v>
+        <v>-238000</v>
       </c>
       <c r="F83" s="3">
-        <v>11500</v>
+        <v>15400</v>
       </c>
       <c r="G83" s="3">
-        <v>6000</v>
+        <v>8100</v>
       </c>
       <c r="H83" s="3">
-        <v>2200</v>
+        <v>2800</v>
       </c>
       <c r="I83" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="J83" s="3" t="s">
         <v>3</v>
@@ -3104,19 +3104,19 @@
         <v>3800</v>
       </c>
       <c r="E89" s="3">
-        <v>-70700</v>
+        <v>13400</v>
       </c>
       <c r="F89" s="3">
-        <v>-27800</v>
+        <v>-37700</v>
       </c>
       <c r="G89" s="3">
-        <v>2400</v>
+        <v>3400</v>
       </c>
       <c r="H89" s="3">
-        <v>-600</v>
+        <v>-1200</v>
       </c>
       <c r="I89" s="3">
-        <v>-5200</v>
+        <v>-6200</v>
       </c>
       <c r="J89" s="3" t="s">
         <v>3</v>
@@ -3152,19 +3152,19 @@
         <v>-1100</v>
       </c>
       <c r="E91" s="3">
-        <v>-87400</v>
+        <v>-108000</v>
       </c>
       <c r="F91" s="3">
-        <v>-126400</v>
+        <v>-171200</v>
       </c>
       <c r="G91" s="3">
-        <v>-1800</v>
+        <v>-2500</v>
       </c>
       <c r="H91" s="3">
-        <v>-15000</v>
+        <v>-19900</v>
       </c>
       <c r="I91" s="3">
-        <v>-2900</v>
+        <v>-3400</v>
       </c>
       <c r="J91" s="3" t="s">
         <v>3</v>
@@ -3251,19 +3251,19 @@
         <v>-1100</v>
       </c>
       <c r="E94" s="3">
-        <v>5500</v>
+        <v>-97300</v>
       </c>
       <c r="F94" s="3">
-        <v>-137600</v>
+        <v>-186300</v>
       </c>
       <c r="G94" s="3">
-        <v>-1100</v>
+        <v>-1400</v>
       </c>
       <c r="H94" s="3">
-        <v>-16700</v>
+        <v>-21800</v>
       </c>
       <c r="I94" s="3">
-        <v>-3900</v>
+        <v>-4500</v>
       </c>
       <c r="J94" s="3" t="s">
         <v>3</v>
@@ -3431,19 +3431,19 @@
         <v>-15800</v>
       </c>
       <c r="E100" s="3">
-        <v>68100</v>
+        <v>84200</v>
       </c>
       <c r="F100" s="3">
-        <v>175100</v>
+        <v>237100</v>
       </c>
       <c r="G100" s="3">
         <v>600</v>
       </c>
       <c r="H100" s="3">
-        <v>1100</v>
+        <v>1400</v>
       </c>
       <c r="I100" s="3">
-        <v>25500</v>
+        <v>32500</v>
       </c>
       <c r="J100" s="3" t="s">
         <v>3</v>
@@ -3464,7 +3464,7 @@
         <v>400</v>
       </c>
       <c r="E101" s="3">
-        <v>1900</v>
+        <v>3900</v>
       </c>
       <c r="F101" s="3" t="s">
         <v>3</v>
@@ -3497,22 +3497,22 @@
         <v>-12600</v>
       </c>
       <c r="E102" s="3">
-        <v>4900</v>
+        <v>4200</v>
       </c>
       <c r="F102" s="3">
-        <v>9800</v>
+        <v>13200</v>
       </c>
       <c r="G102" s="3">
-        <v>1900</v>
+        <v>2600</v>
       </c>
       <c r="H102" s="3">
-        <v>-16200</v>
+        <v>-21500</v>
       </c>
       <c r="I102" s="3">
-        <v>16400</v>
-      </c>
-      <c r="J102" s="3" t="s">
-        <v>3</v>
+        <v>21800</v>
+      </c>
+      <c r="J102" s="3">
+        <v>0</v>
       </c>
       <c r="K102" s="3" t="s">
         <v>3</v>

--- a/AAII_Financials/Yearly/ARBK_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ARBK_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="92">
   <si>
     <t>ARBK</t>
   </si>
@@ -656,160 +656,174 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:N102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="12" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
-        <v>44561</v>
-      </c>
       <c r="G7" s="2">
+        <v>44562</v>
+      </c>
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="K7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="M7" s="2"/>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N7" s="2"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>47000</v>
+      </c>
+      <c r="E8" s="3">
         <v>50600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>58600</v>
       </c>
-      <c r="F8" s="3">
-        <v>100500</v>
-      </c>
       <c r="G8" s="3">
+        <v>98700</v>
+      </c>
+      <c r="H8" s="3">
         <v>25900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>11400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1000</v>
       </c>
-      <c r="J8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M8" s="3"/>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N8" s="3"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>31400</v>
+      </c>
+      <c r="E9" s="3">
         <v>29300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>27800</v>
       </c>
-      <c r="F9" s="3">
-        <v>31000</v>
-      </c>
       <c r="G9" s="3">
+        <v>16100</v>
+      </c>
+      <c r="H9" s="3">
         <v>15400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>4600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1500</v>
       </c>
-      <c r="J9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M9" s="3"/>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N9" s="3"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>15600</v>
+      </c>
+      <c r="E10" s="3">
         <v>21300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>30800</v>
       </c>
-      <c r="F10" s="3">
-        <v>69500</v>
-      </c>
       <c r="G10" s="3">
+        <v>82600</v>
+      </c>
+      <c r="H10" s="3">
         <v>10500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>6800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-500</v>
       </c>
-      <c r="J10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M10" s="3"/>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N10" s="3"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -823,29 +837,30 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E12" s="3">
-        <v>0</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G12" s="3">
-        <v>0</v>
+      <c r="E12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F12" s="3">
+        <v>0</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H12" s="3">
+        <v>0</v>
+      </c>
+      <c r="I12" s="3">
         <v>100</v>
       </c>
-      <c r="I12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J12" s="3" t="s">
         <v>3</v>
       </c>
@@ -855,9 +870,12 @@
       <c r="L12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M12" s="3"/>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N12" s="3"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -888,23 +906,26 @@
       <c r="L13" s="3">
         <v>0</v>
       </c>
-      <c r="M13" s="3"/>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+      <c r="N13" s="3"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>3700</v>
+        <v>33300</v>
       </c>
       <c r="E14" s="3">
-        <v>135100</v>
+        <v>1900</v>
       </c>
       <c r="F14" s="3">
-        <v>500</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
+        <v>183700</v>
+      </c>
+      <c r="G14" s="3">
+        <v>200</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
@@ -921,42 +942,48 @@
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M14" s="3"/>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N14" s="3"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>14200</v>
+      </c>
+      <c r="E15" s="3">
         <v>18700</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>20500</v>
       </c>
-      <c r="F15" s="3">
-        <v>11000</v>
-      </c>
       <c r="G15" s="3">
+        <v>14300</v>
+      </c>
+      <c r="H15" s="3">
         <v>8000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>2800</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>100</v>
       </c>
-      <c r="J15" s="3">
-        <v>0</v>
-      </c>
-      <c r="K15" s="3" t="s">
-        <v>3</v>
+      <c r="K15" s="3">
+        <v>0</v>
       </c>
       <c r="L15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M15" s="3"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N15" s="3"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -967,74 +994,81 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>70000</v>
+        <v>61900</v>
       </c>
       <c r="E17" s="3">
-        <v>139300</v>
+        <v>70300</v>
       </c>
       <c r="F17" s="3">
-        <v>42200</v>
+        <v>85300</v>
       </c>
       <c r="G17" s="3">
+        <v>43600</v>
+      </c>
+      <c r="H17" s="3">
         <v>23300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>12300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>5000</v>
       </c>
-      <c r="J17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M17" s="3"/>
-    </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N17" s="3"/>
+    </row>
+    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-19400</v>
+        <v>-14800</v>
       </c>
       <c r="E18" s="3">
-        <v>-80700</v>
+        <v>-19700</v>
       </c>
       <c r="F18" s="3">
-        <v>58200</v>
+        <v>-26700</v>
       </c>
       <c r="G18" s="3">
+        <v>55100</v>
+      </c>
+      <c r="H18" s="3">
         <v>2600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-3700</v>
       </c>
-      <c r="J18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M18" s="3"/>
-    </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N18" s="3"/>
+    </row>
+    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1048,97 +1082,104 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+    </row>
+    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E20" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F20" s="3">
+        <v>7600</v>
+      </c>
+      <c r="G20" s="3">
+        <v>1600</v>
+      </c>
+      <c r="H20" s="3">
         <v>400</v>
       </c>
-      <c r="E20" s="3">
-        <v>2300</v>
-      </c>
-      <c r="F20" s="3">
-        <v>1600</v>
-      </c>
-      <c r="G20" s="3">
-        <v>400</v>
-      </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>1200</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M20" s="3"/>
-    </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N20" s="3"/>
+    </row>
+    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-1100</v>
+        <v>-400</v>
       </c>
       <c r="E21" s="3">
-        <v>-62500</v>
+        <v>-2500</v>
       </c>
       <c r="F21" s="3">
-        <v>67600</v>
+        <v>-13800</v>
       </c>
       <c r="G21" s="3">
+        <v>67900</v>
+      </c>
+      <c r="H21" s="3">
         <v>10200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-4800</v>
       </c>
-      <c r="J21" s="3">
-        <v>0</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
+      <c r="K21" s="3">
+        <v>0</v>
       </c>
       <c r="L21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M21" s="3"/>
-    </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N21" s="3"/>
+    </row>
+    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>6800</v>
+      </c>
+      <c r="E22" s="3">
         <v>11600</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>22700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>2900</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>200</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>100</v>
       </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>3</v>
+      <c r="J22" s="3">
+        <v>0</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>3</v>
@@ -1146,56 +1187,62 @@
       <c r="L22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M22" s="3"/>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N22" s="3"/>
+    </row>
+    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-35000</v>
+        <v>-54800</v>
       </c>
       <c r="E23" s="3">
+        <v>-34600</v>
+      </c>
+      <c r="F23" s="3">
         <v>-240700</v>
       </c>
-      <c r="F23" s="3">
-        <v>53200</v>
-      </c>
       <c r="G23" s="3">
+        <v>50400</v>
+      </c>
+      <c r="H23" s="3">
         <v>2000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-1200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-4800</v>
       </c>
-      <c r="J23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M23" s="3"/>
-    </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N23" s="3"/>
+    </row>
+    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E24" s="3">
+      <c r="D24" s="3">
+        <v>300</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F24" s="3">
         <v>-11700</v>
       </c>
-      <c r="F24" s="3">
-        <v>11500</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>3</v>
+      <c r="G24" s="3">
+        <v>11300</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>3</v>
@@ -1212,9 +1259,12 @@
       <c r="L24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M24" s="3"/>
-    </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N24" s="3"/>
+    </row>
+    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1245,75 +1295,84 @@
       <c r="L25" s="3">
         <v>0</v>
       </c>
-      <c r="M25" s="3"/>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+      <c r="N25" s="3"/>
+    </row>
+    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-35000</v>
+        <v>-55100</v>
       </c>
       <c r="E26" s="3">
+        <v>-34600</v>
+      </c>
+      <c r="F26" s="3">
         <v>-229000</v>
       </c>
-      <c r="F26" s="3">
-        <v>41700</v>
-      </c>
       <c r="G26" s="3">
+        <v>39100</v>
+      </c>
+      <c r="H26" s="3">
         <v>2000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-1200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-4800</v>
       </c>
-      <c r="J26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M26" s="3"/>
-    </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N26" s="3"/>
+    </row>
+    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-35000</v>
+        <v>-55100</v>
       </c>
       <c r="E27" s="3">
+        <v>-34600</v>
+      </c>
+      <c r="F27" s="3">
         <v>-229000</v>
       </c>
-      <c r="F27" s="3">
-        <v>41700</v>
-      </c>
       <c r="G27" s="3">
+        <v>39100</v>
+      </c>
+      <c r="H27" s="3">
         <v>2000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-1100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-4800</v>
       </c>
-      <c r="J27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M27" s="3"/>
-    </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N27" s="3"/>
+    </row>
+    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1344,9 +1403,12 @@
       <c r="L28" s="3">
         <v>0</v>
       </c>
-      <c r="M28" s="3"/>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+      <c r="N28" s="3"/>
+    </row>
+    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1377,9 +1439,12 @@
       <c r="L29" s="3">
         <v>0</v>
       </c>
-      <c r="M29" s="3"/>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3"/>
+    </row>
+    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1410,9 +1475,12 @@
       <c r="L30" s="3">
         <v>0</v>
       </c>
-      <c r="M30" s="3"/>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+      <c r="N30" s="3"/>
+    </row>
+    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1443,75 +1511,84 @@
       <c r="L31" s="3">
         <v>0</v>
       </c>
-      <c r="M31" s="3"/>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+      <c r="N31" s="3"/>
+    </row>
+    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>200</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="F32" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="G32" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="H32" s="3">
         <v>-400</v>
       </c>
-      <c r="E32" s="3">
-        <v>-2300</v>
-      </c>
-      <c r="F32" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-400</v>
-      </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-1200</v>
       </c>
-      <c r="J32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M32" s="3"/>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N32" s="3"/>
+    </row>
+    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-35000</v>
+        <v>-55100</v>
       </c>
       <c r="E33" s="3">
+        <v>-34600</v>
+      </c>
+      <c r="F33" s="3">
         <v>-229000</v>
       </c>
-      <c r="F33" s="3">
-        <v>41700</v>
-      </c>
       <c r="G33" s="3">
+        <v>39100</v>
+      </c>
+      <c r="H33" s="3">
         <v>2000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-1200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-4800</v>
       </c>
-      <c r="J33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M33" s="3"/>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N33" s="3"/>
+    </row>
+    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1542,80 +1619,89 @@
       <c r="L34" s="3">
         <v>0</v>
       </c>
-      <c r="M34" s="3"/>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+      <c r="N34" s="3"/>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-35000</v>
+        <v>-55100</v>
       </c>
       <c r="E35" s="3">
+        <v>-34600</v>
+      </c>
+      <c r="F35" s="3">
         <v>-229000</v>
       </c>
-      <c r="F35" s="3">
-        <v>41700</v>
-      </c>
       <c r="G35" s="3">
+        <v>39100</v>
+      </c>
+      <c r="H35" s="3">
         <v>2000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-1200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-4800</v>
       </c>
-      <c r="J35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M35" s="3"/>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N35" s="3"/>
+    </row>
+    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
-        <v>44561</v>
-      </c>
       <c r="G38" s="2">
+        <v>44562</v>
+      </c>
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="K38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="L38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="M38" s="2"/>
-    </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N38" s="2"/>
+    </row>
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1629,8 +1715,9 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1644,41 +1731,45 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>8600</v>
+      </c>
+      <c r="E41" s="3">
         <v>7400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>20100</v>
       </c>
-      <c r="F41" s="3">
-        <v>16000</v>
-      </c>
       <c r="G41" s="3">
+        <v>15900</v>
+      </c>
+      <c r="H41" s="3">
         <v>2800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>20900</v>
       </c>
-      <c r="J41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K41" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M41" s="3"/>
-    </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N41" s="3"/>
+    </row>
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1709,9 +1800,12 @@
       <c r="L42" s="3">
         <v>0</v>
       </c>
-      <c r="M42" s="3"/>
-    </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3"/>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -1719,32 +1813,35 @@
         <v>2500</v>
       </c>
       <c r="E43" s="3">
+        <v>2500</v>
+      </c>
+      <c r="F43" s="3">
         <v>800</v>
       </c>
-      <c r="F43" s="3">
-        <v>3700</v>
-      </c>
       <c r="G43" s="3">
+        <v>10100</v>
+      </c>
+      <c r="H43" s="3">
         <v>1900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2800</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K43" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M43" s="3"/>
-    </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N43" s="3"/>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1769,38 +1866,41 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
       </c>
-      <c r="M44" s="3"/>
-    </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M44" s="3">
+        <v>0</v>
+      </c>
+      <c r="N44" s="3"/>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>0</v>
+      </c>
+      <c r="E45" s="3">
         <v>3600</v>
       </c>
-      <c r="E45" s="3">
-        <v>400</v>
-      </c>
       <c r="F45" s="3">
-        <v>173600</v>
+        <v>6400</v>
       </c>
       <c r="G45" s="3">
+        <v>109000</v>
+      </c>
+      <c r="H45" s="3">
         <v>6300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1400</v>
       </c>
-      <c r="I45" s="3">
-        <v>0</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>3</v>
+      <c r="J45" s="3">
+        <v>0</v>
       </c>
       <c r="K45" s="3" t="s">
         <v>3</v>
@@ -1808,62 +1908,68 @@
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M45" s="3"/>
-    </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N45" s="3"/>
+    </row>
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>11700</v>
+      </c>
+      <c r="E46" s="3">
         <v>14900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>27300</v>
       </c>
-      <c r="F46" s="3">
-        <v>211100</v>
-      </c>
       <c r="G46" s="3">
+        <v>210400</v>
+      </c>
+      <c r="H46" s="3">
         <v>12100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>4400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>23700</v>
       </c>
-      <c r="J46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K46" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M46" s="3"/>
-    </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N46" s="3"/>
+    </row>
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>300</v>
+      </c>
+      <c r="E47" s="3">
         <v>400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>3300</v>
       </c>
-      <c r="F47" s="3">
-        <v>19300</v>
-      </c>
       <c r="G47" s="3">
-        <v>1900</v>
+        <v>19200</v>
       </c>
       <c r="H47" s="3">
         <v>1900</v>
       </c>
-      <c r="I47" s="3" t="s">
-        <v>3</v>
+      <c r="I47" s="3">
+        <v>1900</v>
       </c>
       <c r="J47" s="3" t="s">
         <v>3</v>
@@ -1874,75 +1980,84 @@
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M47" s="3"/>
-    </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N47" s="3"/>
+    </row>
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E48" s="3">
         <v>59700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>77500</v>
       </c>
-      <c r="F48" s="3">
-        <v>151600</v>
-      </c>
       <c r="G48" s="3">
+        <v>151000</v>
+      </c>
+      <c r="H48" s="3">
         <v>24400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>20400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3100</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K48" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M48" s="3"/>
-    </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N48" s="3"/>
+    </row>
+    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>200</v>
+      </c>
+      <c r="E49" s="3">
         <v>900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>7600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>800</v>
       </c>
-      <c r="J49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K49" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M49" s="3"/>
-    </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N49" s="3"/>
+    </row>
+    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1973,9 +2088,12 @@
       <c r="L50" s="3">
         <v>0</v>
       </c>
-      <c r="M50" s="3"/>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+      <c r="N50" s="3"/>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2006,9 +2124,12 @@
       <c r="L51" s="3">
         <v>0</v>
       </c>
-      <c r="M51" s="3"/>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+      <c r="N51" s="3"/>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2021,27 +2142,30 @@
       <c r="F52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G52" s="3">
+      <c r="G52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H52" s="3">
         <v>5600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>5500</v>
       </c>
-      <c r="I52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K52" s="3">
-        <v>0</v>
+      <c r="K52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L52" s="3">
         <v>0</v>
       </c>
-      <c r="M52" s="3"/>
-    </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M52" s="3">
+        <v>0</v>
+      </c>
+      <c r="N52" s="3"/>
+    </row>
+    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2072,42 +2196,48 @@
       <c r="L53" s="3">
         <v>0</v>
       </c>
-      <c r="M53" s="3"/>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+      <c r="N53" s="3"/>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>19300</v>
+      </c>
+      <c r="E54" s="3">
         <v>75900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>110200</v>
       </c>
-      <c r="F54" s="3">
-        <v>389600</v>
-      </c>
       <c r="G54" s="3">
+        <v>388100</v>
+      </c>
+      <c r="H54" s="3">
         <v>44600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>32700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>27600</v>
       </c>
-      <c r="J54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K54" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M54" s="3"/>
-    </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N54" s="3"/>
+    </row>
+    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2121,8 +2251,9 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2136,29 +2267,30 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E57" s="3">
         <v>2300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3100</v>
       </c>
-      <c r="F57" s="3">
-        <v>13900</v>
-      </c>
       <c r="G57" s="3">
+        <v>20600</v>
+      </c>
+      <c r="H57" s="3">
         <v>700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3300</v>
       </c>
-      <c r="I57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2168,32 +2300,35 @@
       <c r="L57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M57" s="3"/>
-    </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N57" s="3"/>
+    </row>
+    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>900</v>
+      </c>
+      <c r="E58" s="3">
         <v>14300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>11600</v>
       </c>
-      <c r="F58" s="3">
-        <v>31700</v>
-      </c>
       <c r="G58" s="3">
+        <v>31600</v>
+      </c>
+      <c r="H58" s="3">
         <v>4900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1400</v>
       </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>3</v>
+      <c r="J58" s="3">
+        <v>0</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>3</v>
@@ -2201,32 +2336,35 @@
       <c r="L58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M58" s="3"/>
-    </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N58" s="3"/>
+    </row>
+    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>400</v>
+      </c>
+      <c r="E59" s="3">
         <v>2100</v>
       </c>
-      <c r="E59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F59" s="3">
-        <v>21700</v>
-      </c>
-      <c r="G59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H59" s="3">
-        <v>0</v>
+      <c r="F59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G59" s="3">
+        <v>21600</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I59" s="3">
         <v>0</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>3</v>
+      <c r="J59" s="3">
+        <v>0</v>
       </c>
       <c r="K59" s="3" t="s">
         <v>3</v>
@@ -2234,60 +2372,66 @@
       <c r="L59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M59" s="3"/>
-    </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N59" s="3"/>
+    </row>
+    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>9400</v>
+      </c>
+      <c r="E60" s="3">
         <v>27600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>21400</v>
       </c>
-      <c r="F60" s="3">
-        <v>74000</v>
-      </c>
       <c r="G60" s="3">
+        <v>73800</v>
+      </c>
+      <c r="H60" s="3">
         <v>6000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>5300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>300</v>
       </c>
-      <c r="J60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K60" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M60" s="3"/>
-    </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N60" s="3"/>
+    </row>
+    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>39300</v>
+      </c>
+      <c r="E61" s="3">
         <v>48200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>64300</v>
       </c>
-      <c r="F61" s="3">
-        <v>41500</v>
-      </c>
       <c r="G61" s="3">
+        <v>41400</v>
+      </c>
+      <c r="H61" s="3">
         <v>5300</v>
       </c>
-      <c r="H61" s="3">
-        <v>0</v>
-      </c>
       <c r="I61" s="3">
         <v>0</v>
       </c>
@@ -2300,9 +2444,12 @@
       <c r="L61" s="3">
         <v>0</v>
       </c>
-      <c r="M61" s="3"/>
-    </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3"/>
+    </row>
+    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2333,9 +2480,12 @@
       <c r="L62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M62" s="3"/>
-    </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N62" s="3"/>
+    </row>
+    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2366,9 +2516,12 @@
       <c r="L63" s="3">
         <v>0</v>
       </c>
-      <c r="M63" s="3"/>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+      <c r="N63" s="3"/>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2399,9 +2552,12 @@
       <c r="L64" s="3">
         <v>0</v>
       </c>
-      <c r="M64" s="3"/>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+      <c r="N64" s="3"/>
+    </row>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2432,42 +2588,48 @@
       <c r="L65" s="3">
         <v>0</v>
       </c>
-      <c r="M65" s="3"/>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+      <c r="N65" s="3"/>
+    </row>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>48700</v>
+      </c>
+      <c r="E66" s="3">
         <v>75800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>85700</v>
       </c>
-      <c r="F66" s="3">
-        <v>116300</v>
-      </c>
       <c r="G66" s="3">
+        <v>115900</v>
+      </c>
+      <c r="H66" s="3">
         <v>11400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>5300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>300</v>
       </c>
-      <c r="J66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K66" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M66" s="3"/>
-    </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N66" s="3"/>
+    </row>
+    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2481,8 +2643,9 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+    </row>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2513,9 +2676,12 @@
       <c r="L68" s="3">
         <v>0</v>
       </c>
-      <c r="M68" s="3"/>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+      <c r="N68" s="3"/>
+    </row>
+    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2546,9 +2712,12 @@
       <c r="L69" s="3">
         <v>0</v>
       </c>
-      <c r="M69" s="3"/>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+      <c r="N69" s="3"/>
+    </row>
+    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2579,9 +2748,12 @@
       <c r="L70" s="3">
         <v>0</v>
       </c>
-      <c r="M70" s="3"/>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+      <c r="N70" s="3"/>
+    </row>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2612,42 +2784,48 @@
       <c r="L71" s="3">
         <v>0</v>
       </c>
-      <c r="M71" s="3"/>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+      <c r="N71" s="3"/>
+    </row>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-192400</v>
+        <v>-247100</v>
       </c>
       <c r="E72" s="3">
+        <v>-192000</v>
+      </c>
+      <c r="F72" s="3">
         <v>-157300</v>
       </c>
-      <c r="F72" s="3">
-        <v>71500</v>
-      </c>
       <c r="G72" s="3">
+        <v>69800</v>
+      </c>
+      <c r="H72" s="3">
         <v>30000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-6600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-5200</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K72" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M72" s="3"/>
-    </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N72" s="3"/>
+    </row>
+    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2678,9 +2856,12 @@
       <c r="L73" s="3">
         <v>0</v>
       </c>
-      <c r="M73" s="3"/>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+      <c r="N73" s="3"/>
+    </row>
+    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2711,9 +2892,12 @@
       <c r="L74" s="3">
         <v>0</v>
       </c>
-      <c r="M74" s="3"/>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+      <c r="N74" s="3"/>
+    </row>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2744,42 +2928,48 @@
       <c r="L75" s="3">
         <v>0</v>
       </c>
-      <c r="M75" s="3"/>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+      <c r="N75" s="3"/>
+    </row>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-29500</v>
+      </c>
+      <c r="E76" s="3">
         <v>200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>24600</v>
       </c>
-      <c r="F76" s="3">
-        <v>273300</v>
-      </c>
       <c r="G76" s="3">
+        <v>272300</v>
+      </c>
+      <c r="H76" s="3">
         <v>33200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>27500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>27300</v>
       </c>
-      <c r="J76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K76" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M76" s="3"/>
-    </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N76" s="3"/>
+    </row>
+    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2810,80 +3000,89 @@
       <c r="L77" s="3">
         <v>0</v>
       </c>
-      <c r="M77" s="3"/>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+      <c r="N77" s="3"/>
+    </row>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
-        <v>44561</v>
-      </c>
       <c r="G80" s="2">
+        <v>44562</v>
+      </c>
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="K80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="L80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="M80" s="2"/>
-    </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N80" s="2"/>
+    </row>
+    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-35000</v>
+        <v>-55100</v>
       </c>
       <c r="E81" s="3">
+        <v>-34600</v>
+      </c>
+      <c r="F81" s="3">
         <v>-229000</v>
       </c>
-      <c r="F81" s="3">
-        <v>41700</v>
-      </c>
       <c r="G81" s="3">
+        <v>39100</v>
+      </c>
+      <c r="H81" s="3">
         <v>2000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-1200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-4800</v>
       </c>
-      <c r="J81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M81" s="3"/>
-    </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N81" s="3"/>
+    </row>
+    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2897,41 +3096,45 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+    </row>
+    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>-91900</v>
+        <v>14900</v>
       </c>
       <c r="E83" s="3">
-        <v>-238000</v>
+        <v>20000</v>
       </c>
       <c r="F83" s="3">
-        <v>15400</v>
+        <v>28700</v>
       </c>
       <c r="G83" s="3">
+        <v>15300</v>
+      </c>
+      <c r="H83" s="3">
         <v>8100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>2800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>600</v>
       </c>
-      <c r="J83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M83" s="3"/>
-    </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N83" s="3"/>
+    </row>
+    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2962,9 +3165,12 @@
       <c r="L84" s="3">
         <v>0</v>
       </c>
-      <c r="M84" s="3"/>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+      <c r="N84" s="3"/>
+    </row>
+    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2995,9 +3201,12 @@
       <c r="L85" s="3">
         <v>0</v>
       </c>
-      <c r="M85" s="3"/>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+      <c r="N85" s="3"/>
+    </row>
+    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3028,9 +3237,12 @@
       <c r="L86" s="3">
         <v>0</v>
       </c>
-      <c r="M86" s="3"/>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+      <c r="N86" s="3"/>
+    </row>
+    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3061,9 +3273,12 @@
       <c r="L87" s="3">
         <v>0</v>
       </c>
-      <c r="M87" s="3"/>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+      <c r="N87" s="3"/>
+    </row>
+    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3094,42 +3309,48 @@
       <c r="L88" s="3">
         <v>0</v>
       </c>
-      <c r="M88" s="3"/>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+      <c r="N88" s="3"/>
+    </row>
+    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>3800</v>
+        <v>-44800</v>
       </c>
       <c r="E89" s="3">
-        <v>13400</v>
+        <v>-48000</v>
       </c>
       <c r="F89" s="3">
-        <v>-37700</v>
+        <v>-101200</v>
       </c>
       <c r="G89" s="3">
+        <v>-37000</v>
+      </c>
+      <c r="H89" s="3">
         <v>3400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-1200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-6200</v>
       </c>
-      <c r="J89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M89" s="3"/>
-    </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N89" s="3"/>
+    </row>
+    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3143,41 +3364,45 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+    </row>
+    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
+      <c r="D91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-108000</v>
       </c>
-      <c r="F91" s="3">
-        <v>-171200</v>
-      </c>
       <c r="G91" s="3">
+        <v>-188200</v>
+      </c>
+      <c r="H91" s="3">
         <v>-2500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-19900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-3400</v>
       </c>
-      <c r="J91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M91" s="3"/>
-    </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N91" s="3"/>
+    </row>
+    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3208,9 +3433,12 @@
       <c r="L92" s="3">
         <v>0</v>
       </c>
-      <c r="M92" s="3"/>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+      <c r="N92" s="3"/>
+    </row>
+    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3241,42 +3469,48 @@
       <c r="L93" s="3">
         <v>0</v>
       </c>
-      <c r="M93" s="3"/>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+      <c r="N93" s="3"/>
+    </row>
+    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-1100</v>
+        <v>55100</v>
       </c>
       <c r="E94" s="3">
-        <v>-97300</v>
+        <v>50800</v>
       </c>
       <c r="F94" s="3">
-        <v>-186300</v>
+        <v>17300</v>
       </c>
       <c r="G94" s="3">
+        <v>-183100</v>
+      </c>
+      <c r="H94" s="3">
         <v>-1400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-21800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-4500</v>
       </c>
-      <c r="J94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M94" s="3"/>
-    </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N94" s="3"/>
+    </row>
+    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3290,8 +3524,9 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+    </row>
+    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3322,9 +3557,12 @@
       <c r="L96" s="3">
         <v>0</v>
       </c>
-      <c r="M96" s="3"/>
-    </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3"/>
+    </row>
+    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3355,9 +3593,12 @@
       <c r="L97" s="3">
         <v>0</v>
       </c>
-      <c r="M97" s="3"/>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+      <c r="N97" s="3"/>
+    </row>
+    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3388,9 +3629,12 @@
       <c r="L98" s="3">
         <v>0</v>
       </c>
-      <c r="M98" s="3"/>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+      <c r="N98" s="3"/>
+    </row>
+    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3421,56 +3665,62 @@
       <c r="L99" s="3">
         <v>0</v>
       </c>
-      <c r="M99" s="3"/>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+      <c r="N99" s="3"/>
+    </row>
+    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-9300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-15800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>84200</v>
       </c>
-      <c r="F100" s="3">
-        <v>237100</v>
-      </c>
       <c r="G100" s="3">
+        <v>233100</v>
+      </c>
+      <c r="H100" s="3">
         <v>600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>1400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>32500</v>
       </c>
-      <c r="J100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M100" s="3"/>
-    </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N100" s="3"/>
+    </row>
+    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="E101" s="3">
+        <v>300</v>
+      </c>
+      <c r="F101" s="3">
         <v>3900</v>
       </c>
-      <c r="F101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G101" s="3" t="s">
-        <v>3</v>
+      <c r="G101" s="3">
+        <v>200</v>
       </c>
       <c r="H101" s="3" t="s">
         <v>3</v>
@@ -3484,43 +3734,49 @@
       <c r="K101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
-      </c>
-      <c r="M101" s="3"/>
-    </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="L101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M101" s="3">
+        <v>0</v>
+      </c>
+      <c r="N101" s="3"/>
+    </row>
+    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-12600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>4200</v>
       </c>
-      <c r="F102" s="3">
-        <v>13200</v>
-      </c>
       <c r="G102" s="3">
+        <v>13100</v>
+      </c>
+      <c r="H102" s="3">
         <v>2600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-21500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>21800</v>
       </c>
-      <c r="J102" s="3">
-        <v>0</v>
-      </c>
-      <c r="K102" s="3" t="s">
-        <v>3</v>
+      <c r="K102" s="3">
+        <v>0</v>
       </c>
       <c r="L102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M102" s="3"/>
+      <c r="M102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/ARBK_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ARBK_YR_FIN.xlsx
@@ -919,7 +919,7 @@
         <v>33300</v>
       </c>
       <c r="E14" s="3">
-        <v>1900</v>
+        <v>3000</v>
       </c>
       <c r="F14" s="3">
         <v>183700</v>
@@ -1092,7 +1092,7 @@
         <v>-200</v>
       </c>
       <c r="E20" s="3">
-        <v>1500</v>
+        <v>400</v>
       </c>
       <c r="F20" s="3">
         <v>7600</v>
@@ -1128,7 +1128,7 @@
         <v>-400</v>
       </c>
       <c r="E21" s="3">
-        <v>-2500</v>
+        <v>-1500</v>
       </c>
       <c r="F21" s="3">
         <v>-13800</v>
@@ -1524,7 +1524,7 @@
         <v>200</v>
       </c>
       <c r="E32" s="3">
-        <v>-1500</v>
+        <v>-400</v>
       </c>
       <c r="F32" s="3">
         <v>-7600</v>
@@ -2349,7 +2349,7 @@
         <v>400</v>
       </c>
       <c r="E59" s="3">
-        <v>2100</v>
+        <v>2200</v>
       </c>
       <c r="F59" s="3" t="s">
         <v>3</v>

--- a/AAII_Financials/Yearly/ARBK_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ARBK_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="92">
   <si>
     <t>ARBK</t>
   </si>
@@ -656,174 +656,186 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="14" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44562</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="N7" s="2"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="O7" s="2"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>15500</v>
+      </c>
+      <c r="E8" s="3">
         <v>47000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>50600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>58600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>98700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>25900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>11400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1000</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N8" s="3"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O8" s="3"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>12700</v>
+      </c>
+      <c r="E9" s="3">
         <v>31400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>29300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>27800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>16100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>15400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>4600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1500</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N9" s="3"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O9" s="3"/>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E10" s="3">
         <v>15600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>21300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>30800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>82600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>10500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>6800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-500</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N10" s="3"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O10" s="3"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -838,8 +850,9 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -849,21 +862,21 @@
       <c r="E12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F12" s="3">
-        <v>0</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H12" s="3">
-        <v>0</v>
+      <c r="F12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I12" s="3">
+        <v>0</v>
+      </c>
+      <c r="J12" s="3">
         <v>100</v>
       </c>
-      <c r="J12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K12" s="3" t="s">
         <v>3</v>
       </c>
@@ -873,9 +886,12 @@
       <c r="M12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N12" s="3"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O12" s="3"/>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -909,27 +925,30 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-      <c r="N13" s="3"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+      <c r="O13" s="3"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>33300</v>
+        <v>-18300</v>
       </c>
       <c r="E14" s="3">
-        <v>3000</v>
+        <v>35700</v>
       </c>
       <c r="F14" s="3">
+        <v>7900</v>
+      </c>
+      <c r="G14" s="3">
         <v>183700</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>200</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I14" s="3" t="s">
         <v>3</v>
       </c>
@@ -945,45 +964,51 @@
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N14" s="3"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O14" s="3"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E15" s="3">
         <v>14200</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>18700</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>20500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>14300</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>8000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>2800</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>100</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
-      <c r="L15" s="3" t="s">
-        <v>3</v>
+      <c r="L15" s="3">
+        <v>0</v>
       </c>
       <c r="M15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N15" s="3"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O15" s="3"/>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -995,80 +1020,87 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>61900</v>
+        <v>25100</v>
       </c>
       <c r="E17" s="3">
-        <v>70300</v>
+        <v>60000</v>
       </c>
       <c r="F17" s="3">
+        <v>65300</v>
+      </c>
+      <c r="G17" s="3">
         <v>85300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>43600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>23300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>12300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>5000</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N17" s="3"/>
-    </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O17" s="3"/>
+    </row>
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-9600</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-13000</v>
+      </c>
+      <c r="F18" s="3">
         <v>-14800</v>
       </c>
-      <c r="E18" s="3">
-        <v>-19700</v>
-      </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-26700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>55100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>2600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-3700</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N18" s="3"/>
-    </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O18" s="3"/>
+    </row>
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1083,8 +1115,9 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1092,97 +1125,103 @@
         <v>-200</v>
       </c>
       <c r="E20" s="3">
+        <v>-700</v>
+      </c>
+      <c r="F20" s="3">
         <v>400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>7600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>1600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>1200</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N20" s="3"/>
-    </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O20" s="3"/>
+    </row>
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-400</v>
+        <v>-6800</v>
       </c>
       <c r="E21" s="3">
-        <v>-1500</v>
+        <v>1900</v>
       </c>
       <c r="F21" s="3">
+        <v>3500</v>
+      </c>
+      <c r="G21" s="3">
         <v>-13800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>67900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>10200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-4800</v>
       </c>
-      <c r="K21" s="3">
-        <v>0</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
+      <c r="L21" s="3">
+        <v>0</v>
       </c>
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N21" s="3"/>
-    </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O21" s="3"/>
+    </row>
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E22" s="3">
         <v>6800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>11600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>22700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>2900</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>100</v>
       </c>
-      <c r="J22" s="3">
-        <v>0</v>
-      </c>
-      <c r="K22" s="3" t="s">
-        <v>3</v>
+      <c r="K22" s="3">
+        <v>0</v>
       </c>
       <c r="L22" s="3" t="s">
         <v>3</v>
@@ -1190,63 +1229,69 @@
       <c r="M22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N22" s="3"/>
-    </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O22" s="3"/>
+    </row>
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-54800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-34600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-240700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>50400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>2000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-1200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-4800</v>
       </c>
-      <c r="K23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N23" s="3"/>
-    </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O23" s="3"/>
+    </row>
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E24" s="3">
         <v>300</v>
       </c>
-      <c r="E24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F24" s="3">
+      <c r="F24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G24" s="3">
         <v>-11700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>11300</v>
       </c>
-      <c r="H24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1262,9 +1307,12 @@
       <c r="M24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N24" s="3"/>
-    </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O24" s="3"/>
+    </row>
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1298,81 +1346,90 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-      <c r="N25" s="3"/>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+      <c r="O25" s="3"/>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E26" s="3">
         <v>-55100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-34600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-229000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>39100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>2000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-1200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-4800</v>
       </c>
-      <c r="K26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N26" s="3"/>
-    </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O26" s="3"/>
+    </row>
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E27" s="3">
         <v>-55100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-34600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-229000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>39100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>2000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-1100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-4800</v>
       </c>
-      <c r="K27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N27" s="3"/>
-    </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O27" s="3"/>
+    </row>
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1406,9 +1463,12 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-      <c r="N28" s="3"/>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+      <c r="O28" s="3"/>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1442,9 +1502,12 @@
       <c r="M29" s="3">
         <v>0</v>
       </c>
-      <c r="N29" s="3"/>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3"/>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1478,9 +1541,12 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-      <c r="N30" s="3"/>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+      <c r="O30" s="3"/>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1514,9 +1580,12 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-      <c r="N31" s="3"/>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+      <c r="O31" s="3"/>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1524,71 +1593,77 @@
         <v>200</v>
       </c>
       <c r="E32" s="3">
+        <v>700</v>
+      </c>
+      <c r="F32" s="3">
         <v>-400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-7600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-1600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-1200</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N32" s="3"/>
-    </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O32" s="3"/>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E33" s="3">
         <v>-55100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-34600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-229000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>39100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>2000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-1200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-4800</v>
       </c>
-      <c r="K33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N33" s="3"/>
-    </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O33" s="3"/>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1622,86 +1697,95 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-      <c r="N34" s="3"/>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+      <c r="O34" s="3"/>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E35" s="3">
         <v>-55100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-34600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-229000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>39100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>2000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-1200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-4800</v>
       </c>
-      <c r="K35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N35" s="3"/>
-    </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O35" s="3"/>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44562</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="N38" s="2"/>
-    </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="O38" s="2"/>
+    </row>
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1716,8 +1800,9 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1732,44 +1817,48 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E41" s="3">
         <v>8600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>7400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>20100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>15900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>20900</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L41" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N41" s="3"/>
-    </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O41" s="3"/>
+    </row>
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1803,45 +1892,51 @@
       <c r="M42" s="3">
         <v>0</v>
       </c>
-      <c r="N42" s="3"/>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N42" s="3">
+        <v>0</v>
+      </c>
+      <c r="O42" s="3"/>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>2500</v>
+        <v>600</v>
       </c>
       <c r="E43" s="3">
         <v>2500</v>
       </c>
       <c r="F43" s="3">
+        <v>2500</v>
+      </c>
+      <c r="G43" s="3">
         <v>800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>10100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2800</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L43" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N43" s="3"/>
-    </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O43" s="3"/>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1869,15 +1964,18 @@
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
       </c>
-      <c r="N44" s="3"/>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N44" s="3">
+        <v>0</v>
+      </c>
+      <c r="O44" s="3"/>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -1885,25 +1983,25 @@
         <v>0</v>
       </c>
       <c r="E45" s="3">
+        <v>0</v>
+      </c>
+      <c r="F45" s="3">
         <v>3600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>6400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>109000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>6300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1400</v>
       </c>
-      <c r="J45" s="3">
-        <v>0</v>
-      </c>
-      <c r="K45" s="3" t="s">
-        <v>3</v>
+      <c r="K45" s="3">
+        <v>0</v>
       </c>
       <c r="L45" s="3" t="s">
         <v>3</v>
@@ -1911,68 +2009,74 @@
       <c r="M45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N45" s="3"/>
-    </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O45" s="3"/>
+    </row>
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E46" s="3">
         <v>11700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>14900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>27300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>210400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>12100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>4400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>23700</v>
       </c>
-      <c r="K46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L46" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N46" s="3"/>
-    </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O46" s="3"/>
+    </row>
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="3">
         <v>300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>3300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>19200</v>
-      </c>
-      <c r="H47" s="3">
-        <v>1900</v>
       </c>
       <c r="I47" s="3">
         <v>1900</v>
       </c>
-      <c r="J47" s="3" t="s">
-        <v>3</v>
+      <c r="J47" s="3">
+        <v>1900</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>3</v>
@@ -1983,81 +2087,90 @@
       <c r="M47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N47" s="3"/>
-    </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O47" s="3"/>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>13200</v>
+      </c>
+      <c r="E48" s="3">
         <v>7100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>59700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>77500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>151000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>24400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>20400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3100</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L48" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N48" s="3"/>
-    </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O48" s="3"/>
+    </row>
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E49" s="3">
         <v>200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>7600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>800</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L49" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N49" s="3"/>
-    </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O49" s="3"/>
+    </row>
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2091,9 +2204,12 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-      <c r="N50" s="3"/>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+      <c r="O50" s="3"/>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2127,9 +2243,12 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-      <c r="N51" s="3"/>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+      <c r="O51" s="3"/>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2145,27 +2264,30 @@
       <c r="G52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H52" s="3">
+      <c r="H52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I52" s="3">
         <v>5600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>5500</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L52" s="3">
-        <v>0</v>
+      <c r="L52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M52" s="3">
         <v>0</v>
       </c>
-      <c r="N52" s="3"/>
-    </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N52" s="3">
+        <v>0</v>
+      </c>
+      <c r="O52" s="3"/>
+    </row>
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2199,45 +2321,51 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-      <c r="N53" s="3"/>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+      <c r="O53" s="3"/>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>22700</v>
+      </c>
+      <c r="E54" s="3">
         <v>19300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>75900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>110200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>388100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>44600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>32700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>27600</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L54" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N54" s="3"/>
-    </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O54" s="3"/>
+    </row>
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2252,8 +2380,9 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2268,32 +2397,33 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E57" s="3">
         <v>1700</v>
       </c>
-      <c r="E57" s="3">
-        <v>2300</v>
-      </c>
       <c r="F57" s="3">
+        <v>11200</v>
+      </c>
+      <c r="G57" s="3">
         <v>3100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>20600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3300</v>
       </c>
-      <c r="J57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2303,35 +2433,38 @@
       <c r="M57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N57" s="3"/>
-    </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O57" s="3"/>
+    </row>
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E58" s="3">
         <v>900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>14300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>11600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>31600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>4900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1400</v>
       </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
-      <c r="K58" s="3" t="s">
-        <v>3</v>
+      <c r="K58" s="3">
+        <v>0</v>
       </c>
       <c r="L58" s="3" t="s">
         <v>3</v>
@@ -2339,35 +2472,38 @@
       <c r="M58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N58" s="3"/>
-    </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O58" s="3"/>
+    </row>
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E59" s="3">
         <v>400</v>
       </c>
-      <c r="E59" s="3">
-        <v>2200</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G59" s="3">
+      <c r="F59" s="3">
+        <v>2100</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H59" s="3">
         <v>21600</v>
       </c>
-      <c r="H59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I59" s="3">
-        <v>0</v>
+      <c r="I59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J59" s="3">
         <v>0</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>3</v>
+      <c r="K59" s="3">
+        <v>0</v>
       </c>
       <c r="L59" s="3" t="s">
         <v>3</v>
@@ -2375,66 +2511,72 @@
       <c r="M59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N59" s="3"/>
-    </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O59" s="3"/>
+    </row>
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>8100</v>
+      </c>
+      <c r="E60" s="3">
         <v>9400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>27600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>21400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>73800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>6000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>5300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>300</v>
       </c>
-      <c r="K60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L60" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N60" s="3"/>
-    </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O60" s="3"/>
+    </row>
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E61" s="3">
         <v>39300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>48200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>64300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>41400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>5300</v>
       </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
       <c r="J61" s="3">
         <v>0</v>
       </c>
@@ -2447,9 +2589,12 @@
       <c r="M61" s="3">
         <v>0</v>
       </c>
-      <c r="N61" s="3"/>
-    </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N61" s="3">
+        <v>0</v>
+      </c>
+      <c r="O61" s="3"/>
+    </row>
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2483,9 +2628,12 @@
       <c r="M62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N62" s="3"/>
-    </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O62" s="3"/>
+    </row>
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2519,9 +2667,12 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-      <c r="N63" s="3"/>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+      <c r="O63" s="3"/>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2555,9 +2706,12 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-      <c r="N64" s="3"/>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+      <c r="O64" s="3"/>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2591,45 +2745,51 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-      <c r="N65" s="3"/>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+      <c r="O65" s="3"/>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>9800</v>
+      </c>
+      <c r="E66" s="3">
         <v>48700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>75800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>85700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>115900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>11400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>5300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>300</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L66" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N66" s="3"/>
-    </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O66" s="3"/>
+    </row>
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2644,8 +2804,9 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2679,9 +2840,12 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-      <c r="N68" s="3"/>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+      <c r="O68" s="3"/>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2715,9 +2879,12 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-      <c r="N69" s="3"/>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+      <c r="O69" s="3"/>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2751,9 +2918,12 @@
       <c r="M70" s="3">
         <v>0</v>
       </c>
-      <c r="N70" s="3"/>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+      <c r="O70" s="3"/>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2787,45 +2957,51 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-      <c r="N71" s="3"/>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+      <c r="O71" s="3"/>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-275000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-247100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-192000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-157300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>69800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>30000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-6600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-5200</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L72" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N72" s="3"/>
-    </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O72" s="3"/>
+    </row>
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2859,9 +3035,12 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-      <c r="N73" s="3"/>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+      <c r="O73" s="3"/>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2895,9 +3074,12 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-      <c r="N74" s="3"/>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+      <c r="O74" s="3"/>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2931,45 +3113,51 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-      <c r="N75" s="3"/>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+      <c r="O75" s="3"/>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>12900</v>
+      </c>
+      <c r="E76" s="3">
         <v>-29500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>24600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>272300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>33200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>27500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>27300</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L76" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N76" s="3"/>
-    </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O76" s="3"/>
+    </row>
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3003,86 +3191,95 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-      <c r="N77" s="3"/>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+      <c r="O77" s="3"/>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44562</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="N80" s="2"/>
-    </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="O80" s="2"/>
+    </row>
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E81" s="3">
         <v>-55100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-34600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-229000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>39100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>2000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-1200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-4800</v>
       </c>
-      <c r="K81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N81" s="3"/>
-    </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O81" s="3"/>
+    </row>
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3097,44 +3294,48 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E83" s="3">
         <v>14900</v>
       </c>
-      <c r="E83" s="3">
-        <v>20000</v>
-      </c>
       <c r="F83" s="3">
+        <v>20100</v>
+      </c>
+      <c r="G83" s="3">
         <v>28700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>15300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>8100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>2800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>600</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N83" s="3"/>
-    </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O83" s="3"/>
+    </row>
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3168,9 +3369,12 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-      <c r="N84" s="3"/>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+      <c r="O84" s="3"/>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3204,9 +3408,12 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-      <c r="N85" s="3"/>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+      <c r="O85" s="3"/>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3240,9 +3447,12 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-      <c r="N86" s="3"/>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+      <c r="O86" s="3"/>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3276,9 +3486,12 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-      <c r="N87" s="3"/>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+      <c r="O87" s="3"/>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3312,45 +3525,51 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-      <c r="N88" s="3"/>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+      <c r="O88" s="3"/>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-25000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-44800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-48000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-101200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-37000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>3400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-1200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-6200</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N89" s="3"/>
-    </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O89" s="3"/>
+    </row>
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3365,44 +3584,48 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E91" s="3">
+      <c r="D91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F91" s="3">
         <v>-1100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-108000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-188200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-19900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-3400</v>
       </c>
-      <c r="K91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N91" s="3"/>
-    </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O91" s="3"/>
+    </row>
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3436,9 +3659,12 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-      <c r="N92" s="3"/>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+      <c r="O92" s="3"/>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3472,45 +3698,51 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-      <c r="N93" s="3"/>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+      <c r="O93" s="3"/>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>55100</v>
+        <v>17600</v>
       </c>
       <c r="E94" s="3">
+        <v>55000</v>
+      </c>
+      <c r="F94" s="3">
         <v>50800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>17300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-183100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-21800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-4500</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N94" s="3"/>
-    </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O94" s="3"/>
+    </row>
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3525,8 +3757,9 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3560,9 +3793,12 @@
       <c r="M96" s="3">
         <v>0</v>
       </c>
-      <c r="N96" s="3"/>
-    </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3"/>
+    </row>
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3596,9 +3832,12 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-      <c r="N97" s="3"/>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+      <c r="O97" s="3"/>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3632,9 +3871,12 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-      <c r="N98" s="3"/>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+      <c r="O98" s="3"/>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3668,63 +3910,69 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-      <c r="N99" s="3"/>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+      <c r="O99" s="3"/>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-9300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-15800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>84200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>233100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>1400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>32500</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N100" s="3"/>
-    </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O100" s="3"/>
+    </row>
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>200</v>
+        <v>-100</v>
       </c>
       <c r="E101" s="3">
         <v>300</v>
       </c>
       <c r="F101" s="3">
+        <v>300</v>
+      </c>
+      <c r="G101" s="3">
         <v>3900</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>200</v>
       </c>
-      <c r="H101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I101" s="3" t="s">
         <v>3</v>
       </c>
@@ -3737,46 +3985,52 @@
       <c r="L101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
-      </c>
-      <c r="N101" s="3"/>
-    </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="M101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N101" s="3">
+        <v>0</v>
+      </c>
+      <c r="O101" s="3"/>
+    </row>
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-6400</v>
+      </c>
+      <c r="E102" s="3">
         <v>1200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-12600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>4200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>13100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>2600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-21500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>21800</v>
       </c>
-      <c r="K102" s="3">
-        <v>0</v>
-      </c>
-      <c r="L102" s="3" t="s">
-        <v>3</v>
+      <c r="L102" s="3">
+        <v>0</v>
       </c>
       <c r="M102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N102" s="3"/>
+      <c r="N102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
